--- a/excell/sample_import_product.xlsx
+++ b/excell/sample_import_product.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pionir2\excell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB46D509-5B80-48DD-97AB-FD1ECB5577B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31ABF63-3968-40FC-ACFD-DE7474FF496C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F14D8B50-697F-4B5E-9844-C50405C49856}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -60,9 +60,6 @@
     <t>PPN (PPN / NON PPN)</t>
   </si>
   <si>
-    <t>Berat</t>
-  </si>
-  <si>
     <t>Nama Produk Supplier</t>
   </si>
   <si>
@@ -100,13 +97,55 @@
   </si>
   <si>
     <t>Supplier</t>
+  </si>
+  <si>
+    <t>Berat(Gram)</t>
+  </si>
+  <si>
+    <t>Adaptor 12v 1A HK (Pipih) </t>
+  </si>
+  <si>
+    <t>ALIONG</t>
+  </si>
+  <si>
+    <t>COMVORTA</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>KABEL</t>
+  </si>
+  <si>
+    <t>ALTECH : ADAPTOR 12V / 1A MODEL TIPIS HK : AD003-H ADAPTOR 1A DC 12V</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>NON PPN</t>
+  </si>
+  <si>
+    <t>(T-SDM) ATAS BELAKANG  /  RUMAH E1</t>
+  </si>
+  <si>
+    <t>Jack Akai Mono MAX Hitam
+mono
+warna hitam
+kantong biru</t>
+  </si>
+  <si>
+    <t>Jack Akai Mono MAX Hitam Jack Akai MAX Hitam Jack Akai MAX Mono Jack MAX Jack Akai Mono Super MAX Black Tembaga Biru Jack Akai Mono Max Black (B/O) DY 1223</t>
+  </si>
+  <si>
+    <t>Colokan.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,16 +153,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -131,12 +182,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,96 +527,161 @@
   <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="68.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.140625" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" customWidth="1"/>
+    <col min="14" max="14" width="152" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.42578125" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" customWidth="1"/>
-    <col min="17" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.42578125" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" style="5" customWidth="1"/>
+    <col min="17" max="18" width="15.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.42578125" style="5" customWidth="1"/>
     <col min="20" max="20" width="21.85546875" customWidth="1"/>
     <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="K2">
+        <v>12</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="5">
+        <v>50000</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>60000</v>
+      </c>
+      <c r="R2" s="5">
+        <v>70000</v>
+      </c>
+      <c r="S2" s="5">
+        <v>80000</v>
+      </c>
+      <c r="T2" s="5">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
+      <c r="U2" s="5">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
